--- a/BWL/Übung/Übungen/UE0806_Investitionsrechnung/BWL2T2_07_UE08_Vorlage2.xlsx
+++ b/BWL/Übung/Übungen/UE0806_Investitionsrechnung/BWL2T2_07_UE08_Vorlage2.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="UE 08.1" sheetId="1" state="visible" r:id="rId2"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
   <si>
     <t>UE08.1</t>
   </si>
@@ -453,17 +453,64 @@
     <t xml:space="preserve">Jährlicher Cashflow</t>
   </si>
   <si>
+    <t>Nettobarwert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berücksichtigung Liquiditionserlös</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NBW + Liquiditionserlös</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interpretation: Ohne Berücksichtigung des Liquiditionserlös lohnt sich die Investition nur bei 4% Zinsen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ansonsten lohnt sich die Investition bei 4, 6, und 8% Zinsen, jedoch nicht bei 10 % Zinsen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unterschied Nettobarwert und Barwert</t>
+  </si>
+  <si>
     <t>UE08.5</t>
+  </si>
+  <si>
+    <t>Liquidiationserlös</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cashflow Jahr 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">// Cashflow + Liquiditionserlös</t>
+  </si>
+  <si>
+    <t>Effektivverzinsung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NBW (als Test)</t>
+  </si>
+  <si>
+    <t>b)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variante 2 ist besser. Dadurch dass der interne Zinsfuß höher ist, ist der Gesamtgewinn höher.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Das ist vor allem deshalb so, weil die Cashflows bei Variante 2 eher in den ersten Jahren gemacht werden,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dadurch werden diese Cashflows weniger abgezinst.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0_-;\-&quot;€&quot;\ * #,##0_-;_-&quot;€&quot;\ * &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="&quot;€&quot;\ #,##0"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.00\ [$€-407]_-;\-* #,##0.00\ [$€-407]_-;_-* &quot;-&quot;??\ [$€-407]_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="#,##0.00\ [$€-407]"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -564,7 +611,7 @@
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
     <xf fontId="0" fillId="3" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
@@ -580,9 +627,6 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="10" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="1" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1"/>
@@ -590,6 +634,14 @@
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="1" applyFill="1"/>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="166" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="9" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="20% - Accent1" xfId="1" builtinId="30"/>
@@ -639,7 +691,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Hinterholzer Stefan" id="{73A8AD53-9BED-515D-C891-AFD4EE022FEB}" userId="S::P20016@fhooe.at::6a077e09-2621-4617-a214-6a0ae6f4ad8b" providerId="AD"/>
+  <person displayName="Hinterholzer Stefan" id="{587C982B-B6E2-9832-FAD1-57275F39D970}" userId="S::P20016@fhooe.at::6a077e09-2621-4617-a214-6a0ae6f4ad8b" providerId="AD"/>
 </personList>
 </file>
 
@@ -1178,11 +1230,11 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A4" dT="2025-05-27T07:35:55.71Z" personId="{73A8AD53-9BED-515D-C891-AFD4EE022FEB}" id="{FBADFD58-0062-460C-B478-BF0E1A561B1D}" done="0">
+  <threadedComment ref="A4" dT="2025-05-27T07:35:55.71Z" personId="{587C982B-B6E2-9832-FAD1-57275F39D970}" id="{FBADFD58-0062-460C-B478-BF0E1A561B1D}" done="0">
     <text xml:space="preserve">Sie heißen deshalb Erfolgszahlungen weil sie nicht nur zahlungswirksam sondern auch erfolgswirksam sind (d.h. sie verändern das Ergebnis - Gewinn oder Verlust)
 </text>
   </threadedComment>
-  <threadedComment ref="A9" dT="2025-05-27T07:35:55.71Z" personId="{73A8AD53-9BED-515D-C891-AFD4EE022FEB}" id="{9B535F7F-7001-6361-A1B5-D14391AC019A}" done="0">
+  <threadedComment ref="A9" dT="2025-05-27T07:35:55.71Z" personId="{587C982B-B6E2-9832-FAD1-57275F39D970}" id="{9B535F7F-7001-6361-A1B5-D14391AC019A}" done="0">
     <text xml:space="preserve">Sie heißen deshalb Erfolgszahlungen weil sie nicht nur zahlungswirksam sondern auch erfolgswirksam sind (d.h. sie verändern das Ergebnis - Gewinn oder Verlust)
 </text>
   </threadedComment>
@@ -1296,11 +1348,11 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <f>B6+$B$4/$B$5</f>
+        <f t="shared" ref="B12:B15" si="0">B6+$B$4/$B$5</f>
         <v>25000</v>
       </c>
       <c r="C12" s="2">
-        <f>C6+$C$4/$C$5</f>
+        <f t="shared" ref="C12:C15" si="1">C6+$C$4/$C$5</f>
         <v>40000</v>
       </c>
     </row>
@@ -1309,11 +1361,11 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <f>B7+$B$4/$B$5</f>
+        <f t="shared" si="0"/>
         <v>30000</v>
       </c>
       <c r="C13" s="2">
-        <f>C7+$C$4/$C$5</f>
+        <f t="shared" si="1"/>
         <v>35000</v>
       </c>
     </row>
@@ -1322,11 +1374,11 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <f>B8+$B$4/$B$5</f>
+        <f t="shared" si="0"/>
         <v>35000</v>
       </c>
       <c r="C14" s="2">
-        <f>C8+$C$4/$C$5</f>
+        <f t="shared" si="1"/>
         <v>25000</v>
       </c>
     </row>
@@ -1335,11 +1387,11 @@
         <v>14</v>
       </c>
       <c r="B15" s="2">
-        <f>B9+$B$4/$B$5</f>
+        <f t="shared" si="0"/>
         <v>35000</v>
       </c>
       <c r="C15" s="2">
-        <f>C9+$C$4/$C$5</f>
+        <f t="shared" si="1"/>
         <v>25000</v>
       </c>
     </row>
@@ -1657,24 +1709,24 @@
       <c r="A8" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="12" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="9" ht="14.25">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="12" t="s">
         <v>41</v>
       </c>
       <c r="B9" s="4">
@@ -1722,7 +1774,7 @@
       <c r="A11" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="13">
         <v>0.080000000000000002</v>
       </c>
     </row>
@@ -1730,23 +1782,23 @@
       <c r="A14" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="14">
         <f>B9/(1+$B$11)^B10</f>
         <v>23148.148148148146</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="14">
         <f>C9/(1+$B$11)^C10</f>
         <v>21433.470507544578</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="14">
         <f>D9/(1+$B$11)^D10</f>
         <v>27784.12843570593</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="14">
         <f>E9/(1+$B$11)^E10</f>
         <v>25726.044847875863</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="14">
         <f>F9/(1+$B$11)^F10</f>
         <v>6805.8319703375291</v>
       </c>
@@ -1755,7 +1807,7 @@
       <c r="A16" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="14">
         <f>SUM(B14:F14)</f>
         <v>104897.62390961206</v>
       </c>
@@ -1772,7 +1824,7 @@
       <c r="A18" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="14">
         <f>B16-B17</f>
         <v>4897.6239096120553</v>
       </c>
@@ -1798,9 +1850,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="16.88671875"/>
+    <col bestFit="1" customWidth="1" min="1" max="1" width="29.58203125"/>
+    <col bestFit="1" min="2" max="5" width="13.28125"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1812,83 +1865,162 @@
       <c r="A3" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="16">
+      <c r="B3" s="15">
         <v>200000</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="16"/>
+      <c r="B4" s="15"/>
     </row>
     <row r="5" ht="15.6">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="G5" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H5" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="I5" s="17" t="s">
+      <c r="I5" s="16" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="18">
         <v>32000</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="18">
         <v>32000</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="18">
         <v>32000</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="18">
         <v>32000</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="18">
         <v>32000</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="18">
         <v>32000</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="18">
         <v>32000</v>
       </c>
-      <c r="I6" s="19">
+      <c r="I6" s="18">
         <v>32000</v>
       </c>
+      <c r="L6" s="15"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="19">
         <v>0.040000000000000001</v>
       </c>
       <c r="C8" s="20">
-        <v>0.059999999999999998</v>
-      </c>
-      <c r="D8" s="20">
+        <v>0.058299999999999998</v>
+      </c>
+      <c r="D8" s="19">
         <v>0.080000000000000002</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="19">
         <v>0.10000000000000001</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="A10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="21">
+        <f>NPV(B8,$B$6:$I$6)</f>
+        <v>215447.83599841272</v>
+      </c>
+      <c r="C10" s="21">
+        <f>NPV(C8,$B$6:$I$6)</f>
+        <v>200057.30481711807</v>
+      </c>
+      <c r="D10" s="21">
+        <f>NPV(D8,$B$6:$I$6)</f>
+        <v>183892.44619920955</v>
+      </c>
+      <c r="E10" s="21">
+        <f>NPV(E8,$B$6:$I$6)</f>
+        <v>170717.63833288525</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="22">
+        <f>30000/(1+B8)^8</f>
+        <v>21920.706150059512</v>
+      </c>
+      <c r="C11" s="22">
+        <f>30000/(1+C8)^8</f>
+        <v>19065.617933589383</v>
+      </c>
+      <c r="D11" s="22">
+        <f>30000/(1+D8)^8</f>
+        <v>16208.066535059272</v>
+      </c>
+      <c r="E11" s="22">
+        <f>30000/(1+E8)^8</f>
+        <v>13995.221406291992</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="A12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="21">
+        <f>SUM(B10:B11)</f>
+        <v>237368.54214847222</v>
+      </c>
+      <c r="C12" s="21">
+        <f>SUM(C10:C11)</f>
+        <v>219122.92275070745</v>
+      </c>
+      <c r="D12" s="21">
+        <f>SUM(D10:D11)</f>
+        <v>200100.51273426882</v>
+      </c>
+      <c r="E12" s="21">
+        <f>SUM(E10:E11)</f>
+        <v>184712.85973917725</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25">
+      <c r="B14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="B15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25">
+      <c r="B19" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1901,16 +2033,16 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="12.44140625"/>
+    <col customWidth="1" min="1" max="1" width="17.140625"/>
     <col customWidth="1" min="2" max="2" width="14"/>
-    <col customWidth="1" min="3" max="3" width="11.6640625"/>
+    <col customWidth="1" min="3" max="3" width="14.7109375"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
@@ -1922,6 +2054,147 @@
       </c>
       <c r="C3" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25">
+      <c r="A6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="23">
+        <v>5000</v>
+      </c>
+      <c r="C6" s="23">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25">
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="23">
+        <v>-100000</v>
+      </c>
+      <c r="C8" s="23">
+        <v>-100000</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="23">
+        <v>20000</v>
+      </c>
+      <c r="C9" s="23">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="A10" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="23">
+        <v>20000</v>
+      </c>
+      <c r="C10" s="25">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="A11" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="25">
+        <v>20000</v>
+      </c>
+      <c r="C11" s="25">
+        <v>23000</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="A12" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="25">
+        <v>25000</v>
+      </c>
+      <c r="C12" s="25">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="A13" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="25">
+        <v>25000</v>
+      </c>
+      <c r="C13" s="25">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25">
+      <c r="A14" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" s="25">
+        <f>25000+B6</f>
+        <v>30000</v>
+      </c>
+      <c r="C14" s="25">
+        <f>25000+C6</f>
+        <v>31000</v>
+      </c>
+      <c r="D14" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25">
+      <c r="A17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="13">
+        <f>IRR(B8:B14)</f>
+        <v>0.097676574072629835</v>
+      </c>
+      <c r="C17" s="13">
+        <f>IRR(C8:C14)</f>
+        <v>0.11430471116801129</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25">
+      <c r="A21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21">
+        <f>NPV(B17,B9:B14)</f>
+        <v>100000.00000000006</v>
+      </c>
+      <c r="C21">
+        <f>NPV(C17,C9:C14)</f>
+        <v>100000.00000000001</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25">
+      <c r="A24" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25">
+      <c r="B25" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25">
+      <c r="B26" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/BWL/Übung/Übungen/UE0806_Investitionsrechnung/BWL2T2_07_UE08_Vorlage2.xlsx
+++ b/BWL/Übung/Übungen/UE0806_Investitionsrechnung/BWL2T2_07_UE08_Vorlage2.xlsx
@@ -1,77 +1,72 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr date1904="0"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="4" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
-    <sheet name="UE 08.1" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="UE 08.2" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="UE 08.3." sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="UE 08.4." sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="UE 08.5." sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="UE 08.1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="UE 08.2" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="UE 08.3." sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="UE 08.4." sheetId="4" state="visible" r:id="rId5"/>
+    <sheet name="UE 08.5." sheetId="5" state="visible" r:id="rId6"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
-    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
   </extLst>
 </workbook>
 </file>
 
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={9B535F7F-7001-6361-A1B5-D14391AC019A}</author>
-    <author>tc={FBADFD58-0062-460C-B478-BF0E1A561B1D}</author>
+    <author>tc={00690061-0046-49F9-A54D-001600B900CD}</author>
+    <author>tc={00B50003-0074-4BC0-AC63-0002006900CC}</author>
   </authors>
   <commentList>
-    <comment ref="A4" authorId="1">
+    <comment ref="A4" authorId="0" xr:uid="{00690061-0046-49F9-A54D-001600B900CD}">
       <text>
         <r>
           <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Hinterholzer Stefan:
-</t>
+          <t>tc={FBADFD58-0062-460C-B478-BF0E1A561B1D}:</t>
         </r>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">Sie heißen deshalb Erfolgszahlungen weil sie nicht nur zahlungswirksam sondern auch erfolgswirksam sind (d.h. sie verändern das Ergebnis - Gewinn oder Verlust)
+          <t xml:space="preserve">
+Hinterholzer Stefan:
+Sie heißen deshalb Erfolgszahlungen weil sie nicht nur zahlungswirksam sondern auch erfolgswirksam sind (d.h. sie verändern das Ergebnis - Gewinn oder Verlust)
 </t>
         </r>
       </text>
     </comment>
-    <comment ref="A9" authorId="0">
+    <comment ref="A9" authorId="1" xr:uid="{00B50003-0074-4BC0-AC63-0002006900CC}">
       <text>
         <r>
           <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Hinterholzer Stefan:
-</t>
+          <t>tc={9B535F7F-7001-6361-A1B5-D14391AC019A}:</t>
         </r>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">Sie heißen deshalb Erfolgszahlungen weil sie nicht nur zahlungswirksam sondern auch erfolgswirksam sind (d.h. sie verändern das Ergebnis - Gewinn oder Verlust)
+          <t xml:space="preserve">
+Hinterholzer Stefan:
+Sie heißen deshalb Erfolgszahlungen weil sie nicht nur zahlungswirksam sondern auch erfolgswirksam sind (d.h. sie verändern das Ergebnis - Gewinn oder Verlust)
 </t>
         </r>
       </text>
@@ -81,9 +76,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="75">
-  <si>
-    <t xml:space="preserve">UE08.1</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
+  <si>
+    <t>UE08.1</t>
   </si>
   <si>
     <t xml:space="preserve">in €</t>
@@ -100,8 +95,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Anschaffungswert (I</t>
     </r>
@@ -111,20 +104,16 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0</t>
+      <t>0</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
+      <t>)</t>
     </r>
   </si>
   <si>
@@ -167,10 +156,10 @@
     <t xml:space="preserve">Statische Amortisation</t>
   </si>
   <si>
-    <t xml:space="preserve">UE08.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Einheit</t>
+    <t>UE08.2</t>
+  </si>
+  <si>
+    <t>Einheit</t>
   </si>
   <si>
     <r>
@@ -178,8 +167,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">"Anschaffungswert (I</t>
     </r>
@@ -189,45 +176,41 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0</t>
+      <t>0</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)"</t>
+      <t>)"</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Nutzungsdauer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jahre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Einzahlungen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">€/Stück</t>
+    <t>Nutzungsdauer</t>
+  </si>
+  <si>
+    <t>Jahre</t>
+  </si>
+  <si>
+    <t>Einzahlungen</t>
+  </si>
+  <si>
+    <t>€/Stück</t>
   </si>
   <si>
     <t xml:space="preserve">gesamte Menge pro Jahr</t>
   </si>
   <si>
-    <t xml:space="preserve">Stück</t>
+    <t>Stück</t>
   </si>
   <si>
     <t xml:space="preserve">Fixe Auszahlungen </t>
   </si>
   <si>
-    <t xml:space="preserve">€/Jahr</t>
+    <t>€/Jahr</t>
   </si>
   <si>
     <t xml:space="preserve">variable Auszahlungen</t>
@@ -242,28 +225,28 @@
     <t xml:space="preserve">Cash Flow</t>
   </si>
   <si>
-    <t xml:space="preserve">Amortisationszeit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UE08.3</t>
+    <t>Amortisationszeit</t>
+  </si>
+  <si>
+    <t>UE08.3</t>
   </si>
   <si>
     <t xml:space="preserve">Anschaffungswert 100k</t>
   </si>
   <si>
-    <t xml:space="preserve">t1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">t2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">t3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">t4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">t5</t>
+    <t>t1</t>
+  </si>
+  <si>
+    <t>t2</t>
+  </si>
+  <si>
+    <t>t3</t>
+  </si>
+  <si>
+    <t>t4</t>
+  </si>
+  <si>
+    <t>t5</t>
   </si>
   <si>
     <t xml:space="preserve">Auszahlungen (Erfolgszahlungen)</t>
@@ -272,10 +255,10 @@
     <t xml:space="preserve">Ermittlung Cashflow</t>
   </si>
   <si>
-    <t xml:space="preserve">Jahr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zinssatz</t>
+    <t>Jahr</t>
+  </si>
+  <si>
+    <t>Zinssatz</t>
   </si>
   <si>
     <t xml:space="preserve">Diskontierter Cashflow</t>
@@ -284,13 +267,13 @@
     <t xml:space="preserve">Summe diskontierter Cashflow</t>
   </si>
   <si>
-    <t xml:space="preserve">Anschaffungswert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kapitalwert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UE08.4</t>
+    <t>Anschaffungswert</t>
+  </si>
+  <si>
+    <t>Kapitalwert</t>
+  </si>
+  <si>
+    <t>UE08.4</t>
   </si>
   <si>
     <r>
@@ -298,10 +281,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">t</t>
+      <t>t</t>
     </r>
     <r>
       <rPr>
@@ -309,10 +290,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t>1</t>
     </r>
   </si>
   <si>
@@ -321,10 +300,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">t</t>
+      <t>t</t>
     </r>
     <r>
       <rPr>
@@ -332,10 +309,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
+      <t>2</t>
     </r>
   </si>
   <si>
@@ -344,10 +319,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">t</t>
+      <t>t</t>
     </r>
     <r>
       <rPr>
@@ -355,10 +328,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3</t>
+      <t>3</t>
     </r>
   </si>
   <si>
@@ -367,10 +338,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">t</t>
+      <t>t</t>
     </r>
     <r>
       <rPr>
@@ -378,10 +347,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">4</t>
+      <t>4</t>
     </r>
   </si>
   <si>
@@ -390,10 +357,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">t</t>
+      <t>t</t>
     </r>
     <r>
       <rPr>
@@ -401,10 +366,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">5</t>
+      <t>5</t>
     </r>
   </si>
   <si>
@@ -413,10 +376,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">t</t>
+      <t>t</t>
     </r>
     <r>
       <rPr>
@@ -424,10 +385,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t>6</t>
     </r>
   </si>
   <si>
@@ -436,10 +395,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">t</t>
+      <t>t</t>
     </r>
     <r>
       <rPr>
@@ -447,10 +404,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t>7</t>
     </r>
   </si>
   <si>
@@ -459,10 +414,8 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">t</t>
+      <t>t</t>
     </r>
     <r>
       <rPr>
@@ -470,17 +423,15 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t>8</t>
     </r>
   </si>
   <si>
     <t xml:space="preserve">Jährlicher Cashflow</t>
   </si>
   <si>
-    <t xml:space="preserve">Nettobarwert</t>
+    <t>Nettobarwert</t>
   </si>
   <si>
     <t xml:space="preserve">Berücksichtigung Liquiditionserlös</t>
@@ -498,10 +449,10 @@
     <t xml:space="preserve">Unterschied Nettobarwert und Barwert</t>
   </si>
   <si>
-    <t xml:space="preserve">UE08.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liquidiationserlös</t>
+    <t>UE08.5</t>
+  </si>
+  <si>
+    <t>Liquidiationserlös</t>
   </si>
   <si>
     <t xml:space="preserve">Cashflow Jahr 6</t>
@@ -510,13 +461,13 @@
     <t xml:space="preserve">// Cashflow + Liquiditionserlös</t>
   </si>
   <si>
-    <t xml:space="preserve">Effektivverzinsung</t>
+    <t>Effektivverzinsung</t>
   </si>
   <si>
     <t xml:space="preserve">NBW (als Test)</t>
   </si>
   <si>
-    <t xml:space="preserve">b)</t>
+    <t>b)</t>
   </si>
   <si>
     <t xml:space="preserve">Variante 2 ist besser. Dadurch dass der interne Zinsfuß höher ist, ist der Gesamtgewinn höher.</t>
@@ -531,75 +482,34 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;€ &quot;* #,##0_-;&quot;-€ &quot;* #,##0_-;_-&quot;€ &quot;* \-_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="#,##0"/>
-    <numFmt numFmtId="167" formatCode="_-&quot;€ &quot;* #,##0.00_-;&quot;-€ &quot;* #,##0.00_-;_-&quot;€ &quot;* \-??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="0.00%"/>
-    <numFmt numFmtId="169" formatCode="0"/>
-    <numFmt numFmtId="170" formatCode="&quot;€ &quot;#,##0"/>
-    <numFmt numFmtId="171" formatCode="0%"/>
-    <numFmt numFmtId="172" formatCode="_-* #,##0.00\ [$€-407]_-;\-* #,##0.00\ [$€-407]_-;_-* \-??\ [$€-407]_-;_-@_-"/>
-    <numFmt numFmtId="173" formatCode="#,##0.00\ [$€-407]"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="_-&quot;€ &quot;* #,##0_-;&quot;-€ &quot;* #,##0_-;_-&quot;€ &quot;* \-_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;€ &quot;* #,##0.00_-;&quot;-€ &quot;* #,##0.00_-;_-&quot;€ &quot;* \-??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="&quot;€ &quot;#,##0"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.00\ [$€-407]_-;\-* #,##0.00\ [$€-407]_-;_-* \-??\ [$€-407]_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="#,##0.00\ [$€-407]"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="4">
     <font>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.000000"/>
       <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <b/>
+      <sz val="11.000000"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color theme="0"/>
+      <sz val="11.000000"/>
+      <color indexed="2"/>
       <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <vertAlign val="subscript"/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -611,282 +521,180 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.5999"/>
-        <bgColor rgb="FFC0C0C0"/>
+        <fgColor theme="4" tint="0.59989999999999999"/>
+        <bgColor indexed="22"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.7999"/>
-        <bgColor rgb="FFCCFFFF"/>
+        <fgColor theme="4" tint="0.79990000000000006"/>
+        <bgColor indexed="27"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1"/>
-        <bgColor rgb="FF003300"/>
+        <bgColor indexed="58"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor rgb="FF969696"/>
+        <bgColor indexed="55"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="4">
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
       <top style="thin">
-        <color theme="4" tint="0.3999"/>
+        <color theme="4" tint="0.39989999999999998"/>
       </top>
       <bottom style="thin">
-        <color theme="4" tint="0.3999"/>
+        <color theme="4" tint="0.39989999999999998"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
+    <border>
+      <left style="none"/>
       <right style="thin">
-        <color theme="4" tint="0.3999"/>
+        <color theme="4" tint="0.39989999999999998"/>
       </right>
       <top style="thin">
-        <color theme="4" tint="0.3999"/>
+        <color theme="4" tint="0.39989999999999998"/>
       </top>
       <bottom style="thin">
-        <color theme="4" tint="0.3999"/>
+        <color theme="4" tint="0.39989999999999998"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
     </border>
   </borders>
-  <cellStyleXfs count="22">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
+  <cellStyleXfs count="8">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="43" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="41" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="3" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="22">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="0" xfId="21" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="2" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="3" xfId="0" applyNumberFormat="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="2" fillId="5" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="2" fillId="5" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="3" numFmtId="165" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="10" xfId="0" applyNumberFormat="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="1" xfId="0" applyNumberFormat="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="166" xfId="6" applyNumberFormat="1" applyFill="1" applyProtection="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="7" applyFill="1" applyProtection="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="3" borderId="0" numFmtId="166" xfId="7" applyNumberFormat="1" applyFill="1" applyProtection="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="9" xfId="0" applyNumberFormat="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1" applyProtection="1">
+      <protection hidden="0" locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Excel Built-in 40% - Accent1" xfId="20"/>
-    <cellStyle name="Excel Built-in 20% - Accent1" xfId="21"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
+    <cellStyle name="Excel Built-in 40% - Accent1" xfId="6"/>
+    <cellStyle name="Excel Built-in 20% - Accent1" xfId="7"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF5B9BD5"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFDEEBF7"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFBDD7EE"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF9DC3E6"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="tc={FBADFD58-0062-460C-B478-BF0E1A561B1D}" id="{63C7E678-22C4-6457-5C49-0EF79DFBE663}"/>
+  <person displayName="tc={9B535F7F-7001-6361-A1B5-D14391AC019A}" id="{F4FFD76F-F618-96C6-6DC7-742AFC37E144}"/>
+</personList>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A3:C10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Table1" ref="A3:C10" headerRowCount="1" totalsRowCount="0">
   <autoFilter ref="A3:C10"/>
   <tableColumns count="3">
     <tableColumn id="1" name="in €"/>
@@ -897,7 +705,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table13" displayName="Table13" ref="A3:D9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" displayName="Table13" ref="A3:D9" headerRowCount="1" totalsRowCount="0">
   <autoFilter ref="A3:D9"/>
   <tableColumns count="4">
     <tableColumn id="1" name="in €"/>
@@ -909,7 +717,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table2" displayName="Table2" ref="A8:F11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" displayName="Table2" ref="A8:F11" headerRowCount="1" totalsRowCount="0">
   <autoFilter ref="A8:F11"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Ermittlung Cashflow"/>
@@ -923,7 +731,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table3" displayName="Table3" ref="A3:F5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" displayName="Table3" ref="A3:F5" headerRowCount="1" totalsRowCount="0">
   <autoFilter ref="A3:F5"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Jahre"/>
@@ -936,8 +744,291 @@
 </table>
 </file>
 
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -979,17 +1070,17 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1016,7 +1107,6 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1040,7 +1130,6 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1100,33 +1189,48 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A4" personId="{63C7E678-22C4-6457-5C49-0EF79DFBE663}" id="{00690061-0046-49F9-A54D-001600B900CD}" done="0">
+    <text xml:space="preserve">Hinterholzer Stefan:
+Sie heißen deshalb Erfolgszahlungen weil sie nicht nur zahlungswirksam sondern auch erfolgswirksam sind (d.h. sie verändern das Ergebnis - Gewinn oder Verlust)
+</text>
+  </threadedComment>
+  <threadedComment ref="A9" personId="{F4FFD76F-F618-96C6-6DC7-742AFC37E144}" id="{00B50003-0074-4BC0-AC63-0002006900CC}" done="0">
+    <text xml:space="preserve">Hinterholzer Stefan:
+Sie heißen deshalb Erfolgszahlungen weil sie nicht nur zahlungswirksam sondern auch erfolgswirksam sind (d.h. sie verändern das Ergebnis - Gewinn oder Verlust)
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr filterMode="0">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.11"/>
+    <col customWidth="1" min="1" max="1" style="0" width="21.329999999999998"/>
+    <col customWidth="1" min="2" max="2" style="0" width="17.109999999999999"/>
+    <col customWidth="1" min="3" max="3" style="0" width="18.109999999999999"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="14.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" ht="14.25">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1137,208 +1241,205 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" ht="14.9">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="3">
         <v>100000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="3">
         <v>100000</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" ht="14.25">
+      <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5">
         <v>5</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5">
         <v>5</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" ht="14.25">
+      <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="3">
         <v>5000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" ht="14.25">
+      <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="3">
         <v>10000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="8" ht="14.25">
+      <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="3">
         <v>15000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" ht="14.25">
+      <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="3">
         <v>15000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="10" ht="14.25">
+      <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="3">
         <v>20000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="12" ht="14.25">
+      <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="n">
-        <f aca="false">B6+$B$4/$B$5</f>
+      <c r="B12" s="3">
+        <f t="shared" ref="B12:B15" si="0">B6+$B$4/$B$5</f>
         <v>25000</v>
       </c>
-      <c r="C12" s="3" t="n">
-        <f aca="false">C6+$C$4/$C$5</f>
+      <c r="C12" s="3">
+        <f t="shared" ref="C12:C15" si="1">C6+$C$4/$C$5</f>
         <v>40000</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" ht="14.25">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="n">
-        <f aca="false">B7+$B$4/$B$5</f>
+      <c r="B13" s="3">
+        <f t="shared" si="0"/>
         <v>30000</v>
       </c>
-      <c r="C13" s="3" t="n">
-        <f aca="false">C7+$C$4/$C$5</f>
+      <c r="C13" s="3">
+        <f t="shared" si="1"/>
         <v>35000</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" ht="14.25">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="n">
-        <f aca="false">B8+$B$4/$B$5</f>
+      <c r="B14" s="3">
+        <f t="shared" si="0"/>
         <v>35000</v>
       </c>
-      <c r="C14" s="3" t="n">
-        <f aca="false">C8+$C$4/$C$5</f>
+      <c r="C14" s="3">
+        <f t="shared" si="1"/>
         <v>25000</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" ht="14.25">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="n">
-        <f aca="false">B9+$B$4/$B$5</f>
+      <c r="B15" s="3">
+        <f t="shared" si="0"/>
         <v>35000</v>
       </c>
-      <c r="C15" s="3" t="n">
-        <f aca="false">C9+$C$4/$C$5</f>
+      <c r="C15" s="3">
+        <f t="shared" si="1"/>
         <v>25000</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" ht="14.25">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="n">
-        <f aca="false">B10+$B$4/$B$5</f>
+      <c r="B16" s="3">
+        <f>B10+$B$4/$B$5</f>
         <v>40000</v>
       </c>
-      <c r="C16" s="3" t="n">
-        <f aca="false">C10+$C$4/$C$5</f>
+      <c r="C16" s="3">
+        <f>C10+$C$4/$C$5</f>
         <v>25000</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+    <row r="18" ht="14.25">
+      <c r="A18" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="3" t="n">
-        <f aca="false">AVERAGE(B12:B16)</f>
+      <c r="B18" s="3">
+        <f>AVERAGE(B12:B16)</f>
         <v>33000</v>
       </c>
-      <c r="C18" s="3" t="n">
-        <f aca="false">AVERAGE(C12:C16)</f>
+      <c r="C18" s="3">
+        <f>AVERAGE(C12:C16)</f>
         <v>30000</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+    <row r="20" ht="14.25">
+      <c r="A20" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="0" t="n">
-        <f aca="false">B4/B18</f>
-        <v>3.03030303030303</v>
-      </c>
-      <c r="C20" s="0" t="n">
-        <f aca="false">C4/C18</f>
-        <v>3.33333333333333</v>
+      <c r="B20">
+        <f>B4/B18</f>
+        <v>3.0303030303030298</v>
+      </c>
+      <c r="C20">
+        <f>C4/C18</f>
+        <v>3.3333333333333299</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <tableParts>
+  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter/>
+  <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr filterMode="0">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="29.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="13.22"/>
+    <col customWidth="1" min="1" max="1" style="0" width="29.109999999999999"/>
+    <col customWidth="1" min="2" max="2" style="0" width="13.34"/>
+    <col customWidth="1" min="3" max="4" style="0" width="13.220000000000001"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="14.25">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" ht="14.25">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1352,88 +1453,88 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" ht="14.9">
+      <c r="A4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="3">
         <v>200000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="3">
         <v>100000</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" ht="14.25">
+      <c r="A5" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5">
         <v>10</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5">
         <v>10</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" ht="14.25">
+      <c r="A6" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="3">
         <v>15</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" ht="14.25">
+      <c r="A7" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="4">
         <v>20000</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="4">
         <v>15000</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="8" ht="14.25">
+      <c r="A8" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="3">
         <v>20000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" ht="14.25">
+      <c r="A9" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="5">
         <v>12.5</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="5">
         <v>15</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" ht="14.25">
       <c r="C11" s="6" t="s">
         <v>2</v>
       </c>
@@ -1441,96 +1542,93 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="12" ht="14.25">
+      <c r="A12" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="0" t="n">
-        <f aca="false">C6*C7</f>
+      <c r="C12">
+        <f>C6*C7</f>
         <v>300000</v>
       </c>
-      <c r="D12" s="0" t="n">
-        <f aca="false">D6*D7</f>
+      <c r="D12">
+        <f>D6*D7</f>
         <v>300000</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" ht="14.25">
       <c r="A13" s="8" t="s">
         <v>31</v>
       </c>
       <c r="B13" s="8"/>
-      <c r="C13" s="9" t="n">
-        <f aca="false">C9*C7+C8</f>
+      <c r="C13" s="9">
+        <f>C9*C7+C8</f>
         <v>270000</v>
       </c>
-      <c r="D13" s="9" t="n">
-        <f aca="false">D9*D7+D8</f>
+      <c r="D13" s="9">
+        <f>D9*D7+D8</f>
         <v>255000</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" ht="14.25">
       <c r="A14" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="0" t="n">
-        <f aca="false">C12-C13</f>
+      <c r="C14">
+        <f>C12-C13</f>
         <v>30000</v>
       </c>
-      <c r="D14" s="0" t="n">
-        <f aca="false">D12-D13</f>
+      <c r="D14">
+        <f>D12-D13</f>
         <v>45000</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+    <row r="16" ht="14.25">
+      <c r="A16" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="0" t="n">
-        <f aca="false">C4/C14</f>
-        <v>6.66666666666667</v>
-      </c>
-      <c r="D16" s="0" t="n">
-        <f aca="false">D4/D14</f>
-        <v>2.22222222222222</v>
+      <c r="C16">
+        <f>C4/C14</f>
+        <v>6.6666666666666696</v>
+      </c>
+      <c r="D16">
+        <f>D4/D14</f>
+        <v>2.2222222222222201</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <tableParts>
+  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter/>
+  <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr filterMode="0">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.56"/>
+    <col customWidth="1" min="1" max="1" style="0" width="30.559999999999999"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="14.25">
       <c r="A1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" ht="14.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" ht="14.25">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
@@ -1550,47 +1648,47 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" ht="14.25">
+      <c r="A4" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="4">
         <v>85000</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="4">
         <v>70000</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="4">
         <v>70000</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="4">
         <v>65000</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="4">
         <v>80000</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" ht="14.25">
+      <c r="A5" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="4">
         <v>110000</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="4">
         <v>95000</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="4">
         <v>105000</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="4">
         <v>100000</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="4">
         <v>90000</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" ht="14.25">
       <c r="A8" s="11" t="s">
         <v>42</v>
       </c>
@@ -1610,161 +1708,158 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" ht="14.25">
       <c r="A9" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="4" t="n">
-        <f aca="false">B5-B4</f>
+      <c r="B9" s="4">
+        <f>B5-B4</f>
         <v>25000</v>
       </c>
-      <c r="C9" s="4" t="n">
-        <f aca="false">C5-C4</f>
+      <c r="C9" s="4">
+        <f>C5-C4</f>
         <v>25000</v>
       </c>
-      <c r="D9" s="4" t="n">
-        <f aca="false">D5-D4</f>
+      <c r="D9" s="4">
+        <f>D5-D4</f>
         <v>35000</v>
       </c>
-      <c r="E9" s="4" t="n">
-        <f aca="false">E5-E4</f>
+      <c r="E9" s="4">
+        <f>E5-E4</f>
         <v>35000</v>
       </c>
-      <c r="F9" s="4" t="n">
-        <f aca="false">F5-F4</f>
+      <c r="F9" s="4">
+        <f>F5-F4</f>
         <v>10000</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" ht="14.25">
       <c r="A10" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="4">
         <v>1</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="4">
         <v>2</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="4">
         <v>3</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="4">
         <v>4</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="11" ht="14.25">
+      <c r="A11" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="12" t="n">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="B11" s="12">
+        <v>0.080000000000000002</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25">
+      <c r="A14" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="13" t="n">
-        <f aca="false">B9/(1+$B$11)^B10</f>
-        <v>23148.1481481481</v>
-      </c>
-      <c r="C14" s="13" t="n">
-        <f aca="false">C9/(1+$B$11)^C10</f>
+      <c r="B14" s="13">
+        <f>B9/(1+$B$11)^B10</f>
+        <v>23148.148148148099</v>
+      </c>
+      <c r="C14" s="13">
+        <f>C9/(1+$B$11)^C10</f>
         <v>21433.4705075446</v>
       </c>
-      <c r="D14" s="13" t="n">
-        <f aca="false">D9/(1+$B$11)^D10</f>
-        <v>27784.1284357059</v>
-      </c>
-      <c r="E14" s="13" t="n">
-        <f aca="false">E9/(1+$B$11)^E10</f>
-        <v>25726.0448478759</v>
-      </c>
-      <c r="F14" s="13" t="n">
-        <f aca="false">F9/(1+$B$11)^F10</f>
+      <c r="D14" s="13">
+        <f>D9/(1+$B$11)^D10</f>
+        <v>27784.128435705901</v>
+      </c>
+      <c r="E14" s="13">
+        <f>E9/(1+$B$11)^E10</f>
+        <v>25726.044847875899</v>
+      </c>
+      <c r="F14" s="13">
+        <f>F9/(1+$B$11)^F10</f>
         <v>6805.83197033753</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+    <row r="16" ht="14.25">
+      <c r="A16" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="13" t="n">
-        <f aca="false">SUM(B14:F14)</f>
+      <c r="B16" s="13">
+        <f>SUM(B14:F14)</f>
         <v>104897.623909612</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+    <row r="17" ht="14.25">
+      <c r="A17" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17">
         <v>100000</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+    <row r="18" ht="14.25">
+      <c r="A18" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="13" t="n">
-        <f aca="false">B16-B17</f>
-        <v>4897.62390961206</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D19" s="0" t="n">
-        <f aca="false">NPV(B11,B9:F9)</f>
+      <c r="B18" s="13">
+        <f>B16-B17</f>
+        <v>4897.6239096120598</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25">
+      <c r="D19">
+        <f>NPV(B11,B9:F9)</f>
         <v>104897.623909612</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <legacyDrawing r:id="rId2"/>
-  <tableParts>
-    <tablePart r:id="rId3"/>
+  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId3"/>
+  <tableParts count="2">
     <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr filterMode="0">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="29.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="13.28"/>
+    <col customWidth="1" min="1" max="1" style="0" width="29.59"/>
+    <col customWidth="1" min="2" max="5" style="0" width="13.279999999999999"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="14.25">
       <c r="A1" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" ht="14.25">
+      <c r="A3" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="14" t="n">
+      <c r="B3" s="14">
         <v>200000</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" ht="14.25">
       <c r="B4" s="14"/>
     </row>
-    <row r="5" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="14.9">
       <c r="B5" s="15" t="s">
         <v>50</v>
       </c>
@@ -1790,319 +1885,313 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" ht="14.25">
       <c r="A6" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="17">
         <v>32000</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="17">
         <v>32000</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="17">
         <v>32000</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="17">
         <v>32000</v>
       </c>
-      <c r="F6" s="17" t="n">
+      <c r="F6" s="17">
         <v>32000</v>
       </c>
-      <c r="G6" s="17" t="n">
+      <c r="G6" s="17">
         <v>32000</v>
       </c>
-      <c r="H6" s="17" t="n">
+      <c r="H6" s="17">
         <v>32000</v>
       </c>
-      <c r="I6" s="17" t="n">
+      <c r="I6" s="17">
         <v>32000</v>
       </c>
       <c r="L6" s="14"/>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="8" ht="14.25">
+      <c r="A8" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="18" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="C8" s="18" t="n">
-        <v>0.0583</v>
-      </c>
-      <c r="D8" s="18" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E8" s="18" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="B8" s="18">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="C8" s="18">
+        <v>0.058299999999999998</v>
+      </c>
+      <c r="D8" s="18">
+        <v>0.080000000000000002</v>
+      </c>
+      <c r="E8" s="18">
+        <v>0.10000000000000001</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="A10" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="19" t="n">
-        <f aca="false">NPV(B8,$B$6:$I$6)</f>
-        <v>215447.835998413</v>
-      </c>
-      <c r="C10" s="19" t="n">
-        <f aca="false">NPV(C8,$B$6:$I$6)</f>
-        <v>200057.304817118</v>
-      </c>
-      <c r="D10" s="19" t="n">
-        <f aca="false">NPV(D8,$B$6:$I$6)</f>
-        <v>183892.44619921</v>
-      </c>
-      <c r="E10" s="19" t="n">
-        <f aca="false">NPV(E8,$B$6:$I$6)</f>
-        <v>170717.638332885</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="B10" s="19">
+        <f>NPV(B8,$B$6:$I$6)</f>
+        <v>215447.83599841301</v>
+      </c>
+      <c r="C10" s="19">
+        <f>NPV(C8,$B$6:$I$6)</f>
+        <v>200057.30481711801</v>
+      </c>
+      <c r="D10" s="19">
+        <f>NPV(D8,$B$6:$I$6)</f>
+        <v>183892.44619921001</v>
+      </c>
+      <c r="E10" s="19">
+        <f>NPV(E8,$B$6:$I$6)</f>
+        <v>170717.63833288499</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="A11" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="20" t="n">
-        <f aca="false">30000/(1+B8)^8</f>
-        <v>21920.7061500595</v>
-      </c>
-      <c r="C11" s="20" t="n">
-        <f aca="false">30000/(1+C8)^8</f>
-        <v>19065.6179335894</v>
-      </c>
-      <c r="D11" s="20" t="n">
-        <f aca="false">30000/(1+D8)^8</f>
-        <v>16208.0665350593</v>
-      </c>
-      <c r="E11" s="20" t="n">
-        <f aca="false">30000/(1+E8)^8</f>
-        <v>13995.221406292</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="B11" s="20">
+        <f>30000/(1+B8)^8</f>
+        <v>21920.706150059501</v>
+      </c>
+      <c r="C11" s="20">
+        <f>30000/(1+C8)^8</f>
+        <v>19065.617933589401</v>
+      </c>
+      <c r="D11" s="20">
+        <f>30000/(1+D8)^8</f>
+        <v>16208.066535059301</v>
+      </c>
+      <c r="E11" s="20">
+        <f>30000/(1+E8)^8</f>
+        <v>13995.221406291999</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="A12" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="19" t="n">
-        <f aca="false">SUM(B10:B11)</f>
-        <v>237368.542148472</v>
-      </c>
-      <c r="C12" s="19" t="n">
-        <f aca="false">SUM(C10:C11)</f>
-        <v>219122.922750707</v>
-      </c>
-      <c r="D12" s="19" t="n">
-        <f aca="false">SUM(D10:D11)</f>
+      <c r="B12" s="19">
+        <f>SUM(B10:B11)</f>
+        <v>237368.54214847201</v>
+      </c>
+      <c r="C12" s="19">
+        <f>SUM(C10:C11)</f>
+        <v>219122.92275070699</v>
+      </c>
+      <c r="D12" s="19">
+        <f>SUM(D10:D11)</f>
         <v>200100.512734269</v>
       </c>
-      <c r="E12" s="19" t="n">
-        <f aca="false">SUM(E10:E11)</f>
-        <v>184712.859739177</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
+      <c r="E12" s="19">
+        <f>SUM(E10:E11)</f>
+        <v>184712.85973917699</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25">
+      <c r="B14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="s">
+    <row r="15" ht="14.25">
+      <c r="B15" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="s">
+    <row r="19" ht="14.25">
+      <c r="B19" t="s">
         <v>64</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr filterMode="0">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.88"/>
+    <col customWidth="1" min="1" max="1" style="0" width="17.149999999999999"/>
+    <col customWidth="1" min="2" max="2" style="0" width="14"/>
+    <col customWidth="1" min="3" max="3" style="0" width="14.880000000000001"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="14.25">
       <c r="A1" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" ht="14.25">
+      <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" ht="14.25">
+      <c r="A6" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="20" t="n">
+      <c r="B6" s="20">
         <v>5000</v>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="20">
         <v>6000</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" ht="14.25">
       <c r="B7" s="20"/>
       <c r="C7" s="20"/>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="8" ht="14.25">
+      <c r="A8" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="20" t="n">
+      <c r="B8" s="20">
         <v>-100000</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="20">
         <v>-100000</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" ht="14.25">
+      <c r="A9" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="20" t="n">
+      <c r="B9" s="20">
         <v>20000</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="20">
         <v>25000</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" ht="14.25">
       <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B10" s="20">
         <v>20000</v>
       </c>
-      <c r="C10" s="21" t="n">
+      <c r="C10" s="21">
         <v>25000</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" ht="14.25">
       <c r="A11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="21" t="n">
+      <c r="B11" s="21">
         <v>20000</v>
       </c>
-      <c r="C11" s="21" t="n">
+      <c r="C11" s="21">
         <v>23000</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" ht="14.25">
       <c r="A12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="21" t="n">
+      <c r="B12" s="21">
         <v>25000</v>
       </c>
-      <c r="C12" s="21" t="n">
+      <c r="C12" s="21">
         <v>20000</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" ht="14.25">
       <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="21" t="n">
+      <c r="B13" s="21">
         <v>25000</v>
       </c>
-      <c r="C13" s="21" t="n">
+      <c r="C13" s="21">
         <v>20000</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" ht="14.25">
       <c r="A14" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="21" t="n">
-        <f aca="false">25000+B6</f>
+      <c r="B14" s="21">
+        <f>25000+B6</f>
         <v>30000</v>
       </c>
-      <c r="C14" s="21" t="n">
-        <f aca="false">25000+C6</f>
+      <c r="C14" s="21">
+        <f>25000+C6</f>
         <v>31000</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+    <row r="17" ht="14.25">
+      <c r="A17" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="12" t="n">
-        <f aca="false">IRR(B8:B14)</f>
-        <v>0.0976765740726298</v>
-      </c>
-      <c r="C17" s="12" t="n">
-        <f aca="false">IRR(C8:C14)</f>
+      <c r="B17" s="12">
+        <f>IRR(B8:B14)</f>
+        <v>0.097676574072629793</v>
+      </c>
+      <c r="C17" s="12">
+        <f>IRR(C8:C14)</f>
         <v>0.114304711168011</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+    <row r="21" ht="14.25">
+      <c r="A21" t="s">
         <v>70</v>
       </c>
-      <c r="B21" s="0" t="n">
-        <f aca="false">NPV(B17,B9:B14)</f>
+      <c r="B21">
+        <f>NPV(B17,B9:B14)</f>
         <v>100000</v>
       </c>
-      <c r="C21" s="0" t="n">
-        <f aca="false">NPV(C17,C9:C14)</f>
+      <c r="C21">
+        <f>NPV(C17,C9:C14)</f>
         <v>100000</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+    <row r="24" ht="14.25">
+      <c r="A24" t="s">
         <v>71</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="0" t="s">
+    <row r="25" ht="14.25">
+      <c r="B25" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="0" t="s">
+    <row r="26" ht="14.25">
+      <c r="B26" t="s">
         <v>74</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.51181102362204689" footer="0.51181102362204689"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>